--- a/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_64921_completo.xlsx
+++ b/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_64921_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Red84161fbbbf4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd1ec63e847774444"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7314</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_64921_completo.xlsx
+++ b/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_64921_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd1ec63e847774444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R22b42fc1345b4815"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9101</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0797</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0956</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9969</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9993</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8881</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8987</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8762</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1612</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1614</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8572</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -504,28 +1224,268 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.7582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7461</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.7358</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7464</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7361</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -540,246 +1500,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7517</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7401</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7358</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7494</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7435</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7361</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7428</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7522</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7585</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7562</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7597</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7508</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7509</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7631</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7517</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7461</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>19/07/2026</x:t>
         </x:is>
       </x:c>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0011</x:v>
+        <x:v>      0.9993</x:v>
       </x:c>
     </x:row>
     <x:row>
